--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/4TO_TRIMESTRE/FRACCIONES I-X/FRACC III/LTAIPT_A63F03.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/4TO_TRIMESTRE/FRACCIONES I-X/FRACC III/LTAIPT_A63F03.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9c8ec10a61716621/Documentos/CUARTO PAG WEB/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_81A2AF49F0BFDC4B82D1BA7AC847D41EB3F638DC" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{C47FFEE8-6834-4B4A-B4AF-E2DE83D45512}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -115,283 +121,283 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>19AAEA4F70049E4EC6F3F4C31D8CEA42</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>Dirección General</t>
+  </si>
+  <si>
+    <t>Reglamento Interior del Organismo Público Desconcentrado Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2010%20%20Direccion%20General.docx</t>
+  </si>
+  <si>
+    <t>Subdirección Jurídica</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Unidad de Control Interno</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2051%20Unidad%20de%20Control%20Interno.docx</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2047%20Direcciones%20de%20Plantel.docx</t>
+  </si>
+  <si>
+    <t>Coordinaciones Sectoriales</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2040%20Coordinaciones%20Sectoriales.docx</t>
+  </si>
+  <si>
+    <t>Departamento de Contabilidad</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2037%20Dpto.%20de%20Contabilidad.docx</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2038%20Dpto.%20de%20Programacion%20y%20Presupuesto.docx</t>
+  </si>
+  <si>
+    <t>Departamento de Recuros Materiales y  Servicios Generales</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2034%20Dpto.%20de%20Recursos%20Materiales%20y%20Serv.%20Grales..docx</t>
+  </si>
+  <si>
+    <t>Departamento de Recursos Humanos</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2033%20Dpto.%20de%20Recursos%20Humanos.docx</t>
+  </si>
+  <si>
+    <t>Subdirección Financiera</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2036%20Subdir.%20Financiera.docx</t>
+  </si>
+  <si>
+    <t>Departamento Inventarios</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2035%20Dpto.%20de%20Inventarios.docx</t>
+  </si>
+  <si>
+    <t>Subdirección de Servicios Adminsitrativos</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art,%2032%20Subdir.%20Servicios%20Administrativos.docx</t>
+  </si>
+  <si>
+    <t>Departamento de Actividades Deportivas y Culturales</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2030%20Dpto.%20de%20Activ.%20Deportivas%20y%20culturales.docx</t>
+  </si>
+  <si>
+    <t>Subdirección de Actividades Paraescolares</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.29%20Subdir.%20Actividades%20Paraescolares.docx</t>
+  </si>
+  <si>
+    <t>Departamento de Orientación Educativa y Servicio Social</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2028%20Dpto.%20de%20Orientacion%20Educ.docx</t>
+  </si>
+  <si>
+    <t>Departamento de Control Escolar</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2027%20Dpto.%20Control%20Escolar.docx</t>
+  </si>
+  <si>
+    <t>Subdirección de Servicios Escolares</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2026%20Sub,%20Servicios%20Escolares.docx</t>
+  </si>
+  <si>
+    <t>Subdirección de Seguimiento Académico</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2021%20Subdir.%20Seguimiento%20Academico.docx</t>
+  </si>
+  <si>
+    <t>Dirección Académica</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2020%20Dir.%20Academica.docx</t>
   </si>
   <si>
     <t>Departamento de Información y Relaciones Públicas</t>
   </si>
   <si>
-    <t>Reglamento Interior del Organismo Público Desconcentrado Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
     <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2019%20Dpto.%20de%20Informacion%20y%20rel%20publicas.docx</t>
   </si>
   <si>
-    <t>Subdirección Jurídica</t>
-  </si>
-  <si>
-    <t>12/01/2023</t>
+    <t>Departamento de Planeación e Infraestructura Institucional</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2018%20Dpto.%20de%20Planeacion.docx</t>
+  </si>
+  <si>
+    <t>Subdirección de Planeación y Evaluación Institucional</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2017%20Subdir.%20de%20Planeacion%20y%20Evaluaci%C3%B3n%20Inst..docx</t>
+  </si>
+  <si>
+    <t>Jefes de Materia</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2025%20Jefes%20de%20materia.docx</t>
+  </si>
+  <si>
+    <t>Departamento de Bibliotecas y Laboratorios</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2024%20Dpto.%20de%20Bibliotecas%20y%20laboratorios.docx</t>
+  </si>
+  <si>
+    <t>Departamento de Formación y Desarrollo Docente</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2023%20Dpto.%20de%20formacion%20y%20desarrollo%20docente.docx</t>
+  </si>
+  <si>
+    <t>Departamento de Planes y Programas de Estudio</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2022%20Dpto.%20planes%20de%20estudio.docx</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2015%20Sub.%20Juridica.docx</t>
+  </si>
+  <si>
+    <t>Departamento Jurídico</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2016%20Dpto.%20Juridico.docx</t>
   </si>
   <si>
     <t>10/01/2023</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>5D50FC051554CA1C7631B05CF1CBA1FE</t>
-  </si>
-  <si>
-    <t>Dirección Académica</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2020%20Dir.%20Academica.docx</t>
-  </si>
-  <si>
-    <t>B41F83529AD6CDA90CBB2BD74FA272A0</t>
-  </si>
-  <si>
-    <t>Subdirección de Seguimiento Académico</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2021%20Subdir.%20Seguimiento%20Academico.docx</t>
-  </si>
-  <si>
-    <t>ECE180C7798C31255B1DEC3D2116629B</t>
-  </si>
-  <si>
-    <t>Departamento de Planes y Programas de Estudio</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2022%20Dpto.%20planes%20de%20estudio.docx</t>
-  </si>
-  <si>
-    <t>558A5BF2240EDC12E558F7D8364BC132</t>
-  </si>
-  <si>
-    <t>Departamento de  Formación y Desarrollo Docente</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2023%20Dpto.%20de%20formacion%20y%20desarrollo%20docente.docx</t>
-  </si>
-  <si>
-    <t>174593E600DB1AE3AF9F959C45603DF4</t>
-  </si>
-  <si>
-    <t>Departamento de Bibliotecas y Laboratorios</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2024%20Dpto.%20de%20Bibliotecas%20y%20laboratorios.docx</t>
-  </si>
-  <si>
-    <t>9E452B9F89460086D8A36C65747E2E28</t>
-  </si>
-  <si>
-    <t>Jefes de Materia</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2025%20Jefes%20de%20materia.docx</t>
-  </si>
-  <si>
-    <t>23EE6D35DF42FB884AF431D428453D6E</t>
-  </si>
-  <si>
-    <t>Subdirección de Servicios Escolares</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2026%20Sub,%20Servicios%20Escolares.docx</t>
-  </si>
-  <si>
-    <t>1D7CC0B7283F0B2950DA95FC1691F074</t>
-  </si>
-  <si>
-    <t>Departamento de Control Escolar</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2027%20Dpto.%20Control%20Escolar.docx</t>
-  </si>
-  <si>
-    <t>10F6F6CB9F623B8EA8CAD4A1D7E1E166</t>
-  </si>
-  <si>
-    <t>Departamento de Orientación Educativa y Servicio Social</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2028%20Dpto.%20de%20Orientacion%20Educ.docx</t>
-  </si>
-  <si>
-    <t>42793BAF41FF56B0F4DD6DE1956D14C4</t>
-  </si>
-  <si>
-    <t>Subdirección de Actividades Paraescolares</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.29%20Subdir.%20Actividades%20Paraescolares.docx</t>
-  </si>
-  <si>
-    <t>CBE1C0B3BF31D39E7925A4F1CE215F19</t>
-  </si>
-  <si>
-    <t>Departamento de Actividades Deportivas y Culturales</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2030%20Dpto.%20de%20Activ.%20Deportivas%20y%20culturales.docx</t>
-  </si>
-  <si>
-    <t>EEAEDFDB4ED4C15188A05D8B23F6C939</t>
-  </si>
-  <si>
-    <t>Dirección Administrativa</t>
+    <t>Direcciones de Cada Plantel</t>
+  </si>
+  <si>
+    <t>Departamento de programación y Presupuesto</t>
+  </si>
+  <si>
+    <t>Dirección Adminsitrativa</t>
   </si>
   <si>
     <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2031%20Direcci%C3%B3n%20Admnistrativa.docx</t>
   </si>
   <si>
-    <t>B4991CCA318E03A11663FED257F40688</t>
-  </si>
-  <si>
-    <t>Subdirección de Servicios Administrativos</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art,%2032%20Subdir.%20Servicios%20Administrativos.docx</t>
-  </si>
-  <si>
-    <t>F9AA17C26C89B6B0B5BDE97861FED0E5</t>
-  </si>
-  <si>
-    <t>Departamento de Recursos Humanos</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2033%20Dpto.%20de%20Recursos%20Humanos.docx</t>
-  </si>
-  <si>
-    <t>1516172BA865F04AFDE8E39AFB546A97</t>
-  </si>
-  <si>
-    <t>Departamento de Recursos Materiales y Servicios Generales</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2034%20Dpto.%20de%20Recursos%20Materiales%20y%20Serv.%20Grales..docx</t>
-  </si>
-  <si>
-    <t>5A77A9AF95B2D42DE536ABFEC26E900C</t>
-  </si>
-  <si>
-    <t>Departamento de Inventarios</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2035%20Dpto.%20de%20Inventarios.docx</t>
-  </si>
-  <si>
-    <t>46F258ED1192348AF40C254BC88E8522</t>
-  </si>
-  <si>
-    <t>Subdirección Financiera</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2036%20Subdir.%20Financiera.docx</t>
-  </si>
-  <si>
-    <t>93C36256A9591E34E7124248445BA61B</t>
-  </si>
-  <si>
-    <t>Departamento de Contabilidad</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2037%20Dpto.%20de%20Contabilidad.docx</t>
-  </si>
-  <si>
-    <t>629F342E7D01FE1F62DE6459336E319D</t>
-  </si>
-  <si>
-    <t>Departamento de Programación y Presupuesto</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2038%20Dpto.%20de%20Programacion%20y%20Presupuesto.docx</t>
-  </si>
-  <si>
-    <t>F79BBC938B40ECD0198F400AA6E8E5DD</t>
-  </si>
-  <si>
-    <t>Coordinaciones Sectoriales</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2040%20Coordinaciones%20Sectoriales.docx</t>
-  </si>
-  <si>
-    <t>F67AD6A74EDAC9CEF6E081575BAF0E48</t>
-  </si>
-  <si>
-    <t>Direcciones de cada Plantel</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2047%20Direcciones%20de%20Plantel.docx</t>
-  </si>
-  <si>
-    <t>885BD6AABB50502B640B82F34563313F</t>
-  </si>
-  <si>
-    <t>Unidad de Control Interno</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2051%20Unidad%20de%20Control%20Interno.docx</t>
-  </si>
-  <si>
-    <t>110128AD6B3D1E95DCD30756873224AD</t>
-  </si>
-  <si>
-    <t>Dirección General</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2010%20%20Direccion%20General.docx</t>
-  </si>
-  <si>
-    <t>3DB3243A5C4A4C75EB4CA4FCB45BF5CB</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2015%20Sub.%20Juridica.docx</t>
-  </si>
-  <si>
-    <t>8A3E2AEBD9AE1DC8D17CA13A7DA46021</t>
-  </si>
-  <si>
-    <t>Departamento Jurídico</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2016%20Dpto.%20Juridico.docx</t>
-  </si>
-  <si>
-    <t>EC8866AB21FB93D3FCC6BE818378B359</t>
-  </si>
-  <si>
-    <t>Subdirección de Planeación y Evaluación Institucional</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2017%20Subdir.%20de%20Planeacion%20y%20Evaluaci%C3%B3n%20Inst..docx</t>
-  </si>
-  <si>
-    <t>F25232035CC9FBBF8DD972FF85B30232</t>
-  </si>
-  <si>
-    <t>Departamento de Planeación e Infraestrucura Institucional</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2018%20Dpto.%20de%20Planeacion.docx</t>
+    <t>EB177A86E2487B143E5789CF72A7C1C0</t>
+  </si>
+  <si>
+    <t>01/10/2023</t>
+  </si>
+  <si>
+    <t>31/12/2023</t>
+  </si>
+  <si>
+    <t>27/12/2023</t>
+  </si>
+  <si>
+    <t>16E522967458C7EA7D1FFBCE2EA76835</t>
+  </si>
+  <si>
+    <t>A17A22BA947CA36DF133900F3E034AAB</t>
+  </si>
+  <si>
+    <t>97D42D7DF665145900F72FE3762B9A58</t>
+  </si>
+  <si>
+    <t>D596CD705D05B5AF5F1CE6B07C4022B9</t>
+  </si>
+  <si>
+    <t>A2E9860636C0A765F528F999975208B6</t>
+  </si>
+  <si>
+    <t>D76013077F6C3AF7ACC1AEAE54F63D98</t>
+  </si>
+  <si>
+    <t>7E0FE7905EFFCF5C2FA2D648E61FA57C</t>
+  </si>
+  <si>
+    <t>D0B63C82E5C5828347B7A4E3306CA97E</t>
+  </si>
+  <si>
+    <t>16F8CE69E6FD169AE6DD7E6430ADD9B6</t>
+  </si>
+  <si>
+    <t>FCCA2A69836C87A2A8C217AC063956E1</t>
+  </si>
+  <si>
+    <t>4737D3B84F754D4E18EBFA191F4AAE0B</t>
+  </si>
+  <si>
+    <t>2478855D9496C6B7DE2353A8371D52BC</t>
+  </si>
+  <si>
+    <t>ACD0D382C8310CF430DFC71AC25E7CE1</t>
+  </si>
+  <si>
+    <t>E2332F51A90A9C95AFAFE10A78A2AC6B</t>
+  </si>
+  <si>
+    <t>0376FFF3F43B0D128996CBF949FC8827</t>
+  </si>
+  <si>
+    <t>D9902803D6240EE23E26EC2CEF284121</t>
+  </si>
+  <si>
+    <t>EE12D8255418E2CB3958E7ECE9C4C4E0</t>
+  </si>
+  <si>
+    <t>2E6BB9AEFCF3785A6AC285144E601421</t>
+  </si>
+  <si>
+    <t>B006A64F262B07B2ACE547C70FCE6779</t>
+  </si>
+  <si>
+    <t>58C291878143066C4A4CDA402662930E</t>
+  </si>
+  <si>
+    <t>17F0DFABB88ACA605F6D115E09E3C73A</t>
+  </si>
+  <si>
+    <t>0954CF6BFF8D67989A3110703B022317</t>
+  </si>
+  <si>
+    <t>FEE253254B1F9E8C74DEBCE8F96BE3FA</t>
+  </si>
+  <si>
+    <t>DBB9C552B1001461B8B411CFD83CC8C3</t>
+  </si>
+  <si>
+    <t>806FF904A85B80BFFF7BA555A0BBF63F</t>
+  </si>
+  <si>
+    <t>D4E492EE7D40FC4280230CB76F8095D8</t>
+  </si>
+  <si>
+    <t>38A669362486D0055A30789DAD30AAE0</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -487,6 +493,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -502,44 +511,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -567,14 +576,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -602,6 +628,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -613,179 +656,155 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.5703125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.42578125" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="51.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="51.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="111.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="188" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="73.140625" bestFit="1" customWidth="1"/>
@@ -944,982 +963,982 @@
     </row>
     <row r="8" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>33</v>
+        <v>93</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>44</v>
+        <v>97</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="H11" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>116</v>
+        <v>69</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>123</v>
+        <v>76</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
